--- a/GPTHub_features_template.xlsx
+++ b/GPTHub_features_template.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>OpenWebUI встроенный RAG (эмбеддинги через LiteLLM → mws/bge-m3, pgvector); авто-роутер _sa_doc_qa на mws/glm-4.6 с фокусом на текущий документ</t>
+          <t>Авто-роутер _sa_doc_qa на mws/glm-4.6 с большим контекстным окном. Контекст документа намеренно НЕ сохраняется между сообщениями чата: на каждом запросе учитываются только файлы, прикреплённые к текущему сообщению (memory_function.inlet инжектит &lt;mws_doc_files&gt; из metadata.parent_message.files, сабагент читает их с диска и подаёт в glm-4.6). Это сделано сознательно, чтобы избежать «прилипания» старых документов и утечки чужого контекста в последующие вопросы.</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Частично</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Сабагент sa_presentation реализован как v1-стаб в auto_router_function.py (Phase-9)</t>
+          <t>Отдельный микросервис pptx-service (FastAPI + python-pptx + pypdf + python-docx): POST /build multipart парсит PDF/DOCX/TXT → LiteLLM mws/glm-4.6 в JSON mode (PresentationSchema, max_tokens=4500) → python-pptx рендерит .pptx и стримит байты. Авто-роутер _sa_presentation читает вложение с диска, POSTит в pptx-service, загружает результат в OpenWebUI Files API (loopback + OWUI_ADMIN_TOKEN) и возвращает artifact type=file → в чат приходит 📎 [name.pptx](/api/v1/files/{id}/content). Классификатор: CRITICAL RULE — presentation + safety-net _looks_like_presentation; для follow-up запросов без нового документа в source_text подставляется последние 6 сообщений истории. Graceful fallback на markdown-outline через _presentation_text_fallback (mws/glm-4.6) если pptx-service недоступен, нет OWUI_ADMIN_TOKEN или upload упал. Phase-11 done (2026-04-13).</t>
         </is>
       </c>
     </row>
